--- a/think3d_repro/outputs/run3/vlmeval_runs/SPAgent_4B_no_tools_general/MindCube/SPAgent_4B_no_tools_general_MindCube.xlsx
+++ b/think3d_repro/outputs/run3/vlmeval_runs/SPAgent_4B_no_tools_general/MindCube/SPAgent_4B_no_tools_general_MindCube.xlsx
@@ -3140,7 +3140,7 @@
         <v>1</v>
       </c>
       <c r="I2">
-        <v>10.71094679832458</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3" spans="1:10">
@@ -3169,7 +3169,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>7.892050504684448</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -3198,7 +3198,7 @@
         <v>0</v>
       </c>
       <c r="I4">
-        <v>4.125690221786499</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5" spans="1:10">
@@ -3227,7 +3227,7 @@
         <v>0</v>
       </c>
       <c r="I5">
-        <v>4.222852230072021</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6" spans="1:10">
@@ -3256,7 +3256,7 @@
         <v>0</v>
       </c>
       <c r="I6">
-        <v>5.003349304199219</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -3285,7 +3285,7 @@
         <v>0</v>
       </c>
       <c r="I7">
-        <v>7.062012195587158</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8" spans="1:10">
@@ -3314,7 +3314,7 @@
         <v>1</v>
       </c>
       <c r="I8">
-        <v>13.31405353546143</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -3343,7 +3343,7 @@
         <v>0</v>
       </c>
       <c r="I9">
-        <v>4.703467130661011</v>
+        <v>0</v>
       </c>
     </row>
     <row r="10" spans="1:10">
@@ -3372,7 +3372,7 @@
         <v>1</v>
       </c>
       <c r="I10">
-        <v>4.711602449417114</v>
+        <v>0</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -3401,7 +3401,7 @@
         <v>0</v>
       </c>
       <c r="I11">
-        <v>4.199292421340942</v>
+        <v>0</v>
       </c>
     </row>
     <row r="12" spans="1:10">
@@ -3430,7 +3430,7 @@
         <v>1</v>
       </c>
       <c r="I12">
-        <v>30.36376094818115</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:10">
@@ -3459,7 +3459,7 @@
         <v>0</v>
       </c>
       <c r="I13">
-        <v>28.8605809211731</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:10">
@@ -3488,7 +3488,7 @@
         <v>0</v>
       </c>
       <c r="I14">
-        <v>11.63369107246399</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:10">
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="I15">
-        <v>38.52946257591248</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:10">
@@ -3546,7 +3546,7 @@
         <v>1</v>
       </c>
       <c r="I16">
-        <v>32.4183075428009</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:9">
@@ -3575,7 +3575,7 @@
         <v>0</v>
       </c>
       <c r="I17">
-        <v>7.965658664703369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:9">
@@ -3604,7 +3604,7 @@
         <v>0</v>
       </c>
       <c r="I18">
-        <v>6.658656358718872</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:9">
@@ -3633,7 +3633,7 @@
         <v>0</v>
       </c>
       <c r="I19">
-        <v>6.519165515899658</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:9">
@@ -3662,7 +3662,7 @@
         <v>0</v>
       </c>
       <c r="I20">
-        <v>5.920240879058838</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:9">
@@ -3691,7 +3691,7 @@
         <v>0</v>
       </c>
       <c r="I21">
-        <v>4.169009208679199</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:9">
@@ -3720,7 +3720,7 @@
         <v>0</v>
       </c>
       <c r="I22">
-        <v>35.8210563659668</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:9">
@@ -3749,7 +3749,7 @@
         <v>0</v>
       </c>
       <c r="I23">
-        <v>7.972317695617676</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:9">
@@ -3778,7 +3778,7 @@
         <v>1</v>
       </c>
       <c r="I24">
-        <v>10.58146500587463</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:9">
@@ -3807,7 +3807,7 @@
         <v>0</v>
       </c>
       <c r="I25">
-        <v>5.418231248855591</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:9">
@@ -3836,7 +3836,7 @@
         <v>0</v>
       </c>
       <c r="I26">
-        <v>37.75717926025391</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:9">
@@ -3865,7 +3865,7 @@
         <v>0</v>
       </c>
       <c r="I27">
-        <v>15.74231195449829</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:9">
@@ -3894,7 +3894,7 @@
         <v>1</v>
       </c>
       <c r="I28">
-        <v>34.8950617313385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:9">
@@ -3923,7 +3923,7 @@
         <v>0</v>
       </c>
       <c r="I29">
-        <v>28.05582118034363</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:9">
@@ -3952,7 +3952,7 @@
         <v>0</v>
       </c>
       <c r="I30">
-        <v>7.045054197311401</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:9">
@@ -3981,7 +3981,7 @@
         <v>1</v>
       </c>
       <c r="I31">
-        <v>6.437696933746338</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:9">
@@ -4010,7 +4010,7 @@
         <v>0</v>
       </c>
       <c r="I32">
-        <v>10.5414891242981</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:9">
@@ -4039,7 +4039,7 @@
         <v>1</v>
       </c>
       <c r="I33">
-        <v>5.821779489517212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:9">
@@ -4068,7 +4068,7 @@
         <v>0</v>
       </c>
       <c r="I34">
-        <v>8.629691362380981</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:9">
@@ -4097,7 +4097,7 @@
         <v>1</v>
       </c>
       <c r="I35">
-        <v>32.41030645370483</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:9">
@@ -4126,7 +4126,7 @@
         <v>0</v>
       </c>
       <c r="I36">
-        <v>5.413116931915283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:9">
@@ -4155,7 +4155,7 @@
         <v>0</v>
       </c>
       <c r="I37">
-        <v>34.65165209770203</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:9">
@@ -4184,7 +4184,7 @@
         <v>0</v>
       </c>
       <c r="I38">
-        <v>32.01728105545044</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:9">
@@ -4213,7 +4213,7 @@
         <v>0</v>
       </c>
       <c r="I39">
-        <v>16.00865840911865</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:9">
@@ -4242,7 +4242,7 @@
         <v>0</v>
       </c>
       <c r="I40">
-        <v>5.597021341323853</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:9">
@@ -4271,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="I41">
-        <v>13.6843147277832</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:9">
@@ -4300,7 +4300,7 @@
         <v>0</v>
       </c>
       <c r="I42">
-        <v>4.656522750854492</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:9">
@@ -4329,7 +4329,7 @@
         <v>1</v>
       </c>
       <c r="I43">
-        <v>3.025565624237061</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:9">
@@ -4358,7 +4358,7 @@
         <v>0</v>
       </c>
       <c r="I44">
-        <v>9.821193218231201</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:9">
@@ -4387,7 +4387,7 @@
         <v>1</v>
       </c>
       <c r="I45">
-        <v>3.619378805160522</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:9">
@@ -4416,7 +4416,7 @@
         <v>0</v>
       </c>
       <c r="I46">
-        <v>10.20485210418701</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:9">
@@ -4445,7 +4445,7 @@
         <v>1</v>
       </c>
       <c r="I47">
-        <v>3.991512537002563</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:9">
@@ -4474,7 +4474,7 @@
         <v>1</v>
       </c>
       <c r="I48">
-        <v>6.903319120407104</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:9">
@@ -4503,7 +4503,7 @@
         <v>0</v>
       </c>
       <c r="I49">
-        <v>5.789844036102295</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:9">
@@ -4532,7 +4532,7 @@
         <v>0</v>
       </c>
       <c r="I50">
-        <v>3.946445465087891</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:9">
@@ -4561,7 +4561,7 @@
         <v>0</v>
       </c>
       <c r="I51">
-        <v>4.996031045913696</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:9">
@@ -4590,7 +4590,7 @@
         <v>0</v>
       </c>
       <c r="I52">
-        <v>3.185501337051392</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:9">
@@ -4619,7 +4619,7 @@
         <v>0</v>
       </c>
       <c r="I53">
-        <v>5.965070962905884</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:9">
@@ -4648,7 +4648,7 @@
         <v>0</v>
       </c>
       <c r="I54">
-        <v>4.099239349365234</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:9">
@@ -4677,7 +4677,7 @@
         <v>0</v>
       </c>
       <c r="I55">
-        <v>5.661629438400269</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:9">
@@ -4706,7 +4706,7 @@
         <v>0</v>
       </c>
       <c r="I56">
-        <v>3.554231882095337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:9">
@@ -4735,7 +4735,7 @@
         <v>1</v>
       </c>
       <c r="I57">
-        <v>5.657281398773193</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:9">
@@ -4764,7 +4764,7 @@
         <v>1</v>
       </c>
       <c r="I58">
-        <v>6.061418771743774</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:9">
@@ -4793,7 +4793,7 @@
         <v>1</v>
       </c>
       <c r="I59">
-        <v>2.884654998779297</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:9">
@@ -4822,7 +4822,7 @@
         <v>1</v>
       </c>
       <c r="I60">
-        <v>3.963217258453369</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:9">
@@ -4851,7 +4851,7 @@
         <v>0</v>
       </c>
       <c r="I61">
-        <v>11.42964053153992</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:9">
@@ -4880,7 +4880,7 @@
         <v>0</v>
       </c>
       <c r="I62">
-        <v>4.918236970901489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:9">
@@ -4909,7 +4909,7 @@
         <v>1</v>
       </c>
       <c r="I63">
-        <v>3.927650451660156</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:9">
@@ -4938,7 +4938,7 @@
         <v>0</v>
       </c>
       <c r="I64">
-        <v>5.145192861557007</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:9">
@@ -4967,7 +4967,7 @@
         <v>1</v>
       </c>
       <c r="I65">
-        <v>9.621923208236694</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:9">
@@ -4996,7 +4996,7 @@
         <v>0</v>
       </c>
       <c r="I66">
-        <v>4.193392038345337</v>
+        <v>0</v>
       </c>
     </row>
     <row r="67" spans="1:9">
@@ -5025,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="I67">
-        <v>4.511476755142212</v>
+        <v>0</v>
       </c>
     </row>
     <row r="68" spans="1:9">
@@ -5054,7 +5054,7 @@
         <v>0</v>
       </c>
       <c r="I68">
-        <v>5.925033330917358</v>
+        <v>0</v>
       </c>
     </row>
     <row r="69" spans="1:9">
@@ -5083,7 +5083,7 @@
         <v>1</v>
       </c>
       <c r="I69">
-        <v>7.97270131111145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="70" spans="1:9">
@@ -5112,7 +5112,7 @@
         <v>0</v>
       </c>
       <c r="I70">
-        <v>44.20608115196228</v>
+        <v>0</v>
       </c>
     </row>
     <row r="71" spans="1:9">
@@ -5141,7 +5141,7 @@
         <v>1</v>
       </c>
       <c r="I71">
-        <v>9.605684995651245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="72" spans="1:9">
@@ -5170,7 +5170,7 @@
         <v>1</v>
       </c>
       <c r="I72">
-        <v>3.083400964736938</v>
+        <v>0</v>
       </c>
     </row>
     <row r="73" spans="1:9">
@@ -5199,7 +5199,7 @@
         <v>0</v>
       </c>
       <c r="I73">
-        <v>6.60596752166748</v>
+        <v>0</v>
       </c>
     </row>
     <row r="74" spans="1:9">
@@ -5228,7 +5228,7 @@
         <v>0</v>
       </c>
       <c r="I74">
-        <v>7.324216842651367</v>
+        <v>0</v>
       </c>
     </row>
     <row r="75" spans="1:9">
@@ -5257,7 +5257,7 @@
         <v>0</v>
       </c>
       <c r="I75">
-        <v>6.425790309906006</v>
+        <v>0</v>
       </c>
     </row>
     <row r="76" spans="1:9">
@@ -5286,7 +5286,7 @@
         <v>0</v>
       </c>
       <c r="I76">
-        <v>1.437984228134155</v>
+        <v>0</v>
       </c>
     </row>
     <row r="77" spans="1:9">
@@ -5315,7 +5315,7 @@
         <v>0</v>
       </c>
       <c r="I77">
-        <v>3.896541118621826</v>
+        <v>0</v>
       </c>
     </row>
     <row r="78" spans="1:9">
@@ -5344,7 +5344,7 @@
         <v>0</v>
       </c>
       <c r="I78">
-        <v>4.197566747665405</v>
+        <v>0</v>
       </c>
     </row>
     <row r="79" spans="1:9">
@@ -5373,7 +5373,7 @@
         <v>0</v>
       </c>
       <c r="I79">
-        <v>5.630800485610962</v>
+        <v>0</v>
       </c>
     </row>
     <row r="80" spans="1:9">
@@ -5402,7 +5402,7 @@
         <v>0</v>
       </c>
       <c r="I80">
-        <v>5.050621032714844</v>
+        <v>0</v>
       </c>
     </row>
     <row r="81" spans="1:9">
@@ -5431,7 +5431,7 @@
         <v>0</v>
       </c>
       <c r="I81">
-        <v>3.550684452056885</v>
+        <v>0</v>
       </c>
     </row>
     <row r="82" spans="1:9">
@@ -5460,7 +5460,7 @@
         <v>1</v>
       </c>
       <c r="I82">
-        <v>3.444489240646362</v>
+        <v>0</v>
       </c>
     </row>
     <row r="83" spans="1:9">
@@ -5489,7 +5489,7 @@
         <v>1</v>
       </c>
       <c r="I83">
-        <v>5.540453672409058</v>
+        <v>0</v>
       </c>
     </row>
     <row r="84" spans="1:9">
@@ -5518,7 +5518,7 @@
         <v>0</v>
       </c>
       <c r="I84">
-        <v>6.282600164413452</v>
+        <v>0</v>
       </c>
     </row>
     <row r="85" spans="1:9">
@@ -5547,7 +5547,7 @@
         <v>1</v>
       </c>
       <c r="I85">
-        <v>5.920084953308105</v>
+        <v>0</v>
       </c>
     </row>
     <row r="86" spans="1:9">
@@ -5576,7 +5576,7 @@
         <v>0</v>
       </c>
       <c r="I86">
-        <v>10.39830589294434</v>
+        <v>0</v>
       </c>
     </row>
     <row r="87" spans="1:9">
@@ -5605,7 +5605,7 @@
         <v>0</v>
       </c>
       <c r="I87">
-        <v>6.916068553924561</v>
+        <v>0</v>
       </c>
     </row>
     <row r="88" spans="1:9">
@@ -5634,7 +5634,7 @@
         <v>1</v>
       </c>
       <c r="I88">
-        <v>6.980337858200073</v>
+        <v>0</v>
       </c>
     </row>
     <row r="89" spans="1:9">
@@ -5663,7 +5663,7 @@
         <v>0</v>
       </c>
       <c r="I89">
-        <v>7.068707466125488</v>
+        <v>0</v>
       </c>
     </row>
     <row r="90" spans="1:9">
@@ -5692,7 +5692,7 @@
         <v>1</v>
       </c>
       <c r="I90">
-        <v>10.70626831054688</v>
+        <v>0</v>
       </c>
     </row>
     <row r="91" spans="1:9">
@@ -5721,7 +5721,7 @@
         <v>1</v>
       </c>
       <c r="I91">
-        <v>5.558170557022095</v>
+        <v>0</v>
       </c>
     </row>
     <row r="92" spans="1:9">
@@ -5750,7 +5750,7 @@
         <v>0</v>
       </c>
       <c r="I92">
-        <v>7.112476110458374</v>
+        <v>0</v>
       </c>
     </row>
     <row r="93" spans="1:9">
@@ -5779,7 +5779,7 @@
         <v>0</v>
       </c>
       <c r="I93">
-        <v>14.41950392723083</v>
+        <v>0</v>
       </c>
     </row>
     <row r="94" spans="1:9">
@@ -5808,7 +5808,7 @@
         <v>0</v>
       </c>
       <c r="I94">
-        <v>3.939963579177856</v>
+        <v>0</v>
       </c>
     </row>
     <row r="95" spans="1:9">
@@ -5837,7 +5837,7 @@
         <v>1</v>
       </c>
       <c r="I95">
-        <v>5.615122556686401</v>
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:9">
@@ -5866,7 +5866,7 @@
         <v>0</v>
       </c>
       <c r="I96">
-        <v>11.9468195438385</v>
+        <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:9">
@@ -5895,7 +5895,7 @@
         <v>1</v>
       </c>
       <c r="I97">
-        <v>6.664155006408691</v>
+        <v>0</v>
       </c>
     </row>
     <row r="98" spans="1:9">
@@ -5924,7 +5924,7 @@
         <v>1</v>
       </c>
       <c r="I98">
-        <v>6.260809421539307</v>
+        <v>0</v>
       </c>
     </row>
     <row r="99" spans="1:9">
@@ -5953,7 +5953,7 @@
         <v>0</v>
       </c>
       <c r="I99">
-        <v>6.826935291290283</v>
+        <v>0</v>
       </c>
     </row>
     <row r="100" spans="1:9">
@@ -5982,7 +5982,7 @@
         <v>0</v>
       </c>
       <c r="I100">
-        <v>6.146359205245972</v>
+        <v>0</v>
       </c>
     </row>
     <row r="101" spans="1:9">
@@ -6011,7 +6011,7 @@
         <v>0</v>
       </c>
       <c r="I101">
-        <v>4.858603954315186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="102" spans="1:9">
@@ -6040,7 +6040,7 @@
         <v>1</v>
       </c>
       <c r="I102">
-        <v>10.64866399765015</v>
+        <v>0</v>
       </c>
     </row>
     <row r="103" spans="1:9">
@@ -6069,7 +6069,7 @@
         <v>0</v>
       </c>
       <c r="I103">
-        <v>9.615376472473145</v>
+        <v>0</v>
       </c>
     </row>
     <row r="104" spans="1:9">
@@ -6098,7 +6098,7 @@
         <v>0</v>
       </c>
       <c r="I104">
-        <v>6.942705869674683</v>
+        <v>0</v>
       </c>
     </row>
     <row r="105" spans="1:9">
@@ -6127,7 +6127,7 @@
         <v>0</v>
       </c>
       <c r="I105">
-        <v>10.30509948730469</v>
+        <v>0</v>
       </c>
     </row>
     <row r="106" spans="1:9">
@@ -6156,7 +6156,7 @@
         <v>1</v>
       </c>
       <c r="I106">
-        <v>6.650803327560425</v>
+        <v>0</v>
       </c>
     </row>
     <row r="107" spans="1:9">
@@ -6185,7 +6185,7 @@
         <v>0</v>
       </c>
       <c r="I107">
-        <v>7.697890520095825</v>
+        <v>0</v>
       </c>
     </row>
     <row r="108" spans="1:9">
@@ -6214,7 +6214,7 @@
         <v>0</v>
       </c>
       <c r="I108">
-        <v>39.98308181762695</v>
+        <v>0</v>
       </c>
     </row>
     <row r="109" spans="1:9">
@@ -6243,7 +6243,7 @@
         <v>1</v>
       </c>
       <c r="I109">
-        <v>4.497658014297485</v>
+        <v>0</v>
       </c>
     </row>
     <row r="110" spans="1:9">
@@ -6272,7 +6272,7 @@
         <v>0</v>
       </c>
       <c r="I110">
-        <v>5.053536653518677</v>
+        <v>0</v>
       </c>
     </row>
     <row r="111" spans="1:9">
@@ -6301,7 +6301,7 @@
         <v>0</v>
       </c>
       <c r="I111">
-        <v>7.422343015670776</v>
+        <v>0</v>
       </c>
     </row>
     <row r="112" spans="1:9">
@@ -6330,7 +6330,7 @@
         <v>1</v>
       </c>
       <c r="I112">
-        <v>6.153750419616699</v>
+        <v>0</v>
       </c>
     </row>
     <row r="113" spans="1:9">
@@ -6359,7 +6359,7 @@
         <v>1</v>
       </c>
       <c r="I113">
-        <v>6.702917575836182</v>
+        <v>0</v>
       </c>
     </row>
     <row r="114" spans="1:9">
@@ -6388,7 +6388,7 @@
         <v>0</v>
       </c>
       <c r="I114">
-        <v>5.358493328094482</v>
+        <v>0</v>
       </c>
     </row>
     <row r="115" spans="1:9">
@@ -6417,7 +6417,7 @@
         <v>0</v>
       </c>
       <c r="I115">
-        <v>8.648144960403442</v>
+        <v>0</v>
       </c>
     </row>
     <row r="116" spans="1:9">
@@ -6446,7 +6446,7 @@
         <v>0</v>
       </c>
       <c r="I116">
-        <v>6.455914258956909</v>
+        <v>0</v>
       </c>
     </row>
     <row r="117" spans="1:9">
@@ -6475,7 +6475,7 @@
         <v>0</v>
       </c>
       <c r="I117">
-        <v>9.394778728485107</v>
+        <v>0</v>
       </c>
     </row>
     <row r="118" spans="1:9">
@@ -6504,7 +6504,7 @@
         <v>0</v>
       </c>
       <c r="I118">
-        <v>5.99237847328186</v>
+        <v>0</v>
       </c>
     </row>
     <row r="119" spans="1:9">
@@ -6533,7 +6533,7 @@
         <v>1</v>
       </c>
       <c r="I119">
-        <v>5.330416202545166</v>
+        <v>0</v>
       </c>
     </row>
     <row r="120" spans="1:9">
@@ -6562,7 +6562,7 @@
         <v>0</v>
       </c>
       <c r="I120">
-        <v>10.4536235332489</v>
+        <v>0</v>
       </c>
     </row>
     <row r="121" spans="1:9">
@@ -6591,7 +6591,7 @@
         <v>1</v>
       </c>
       <c r="I121">
-        <v>15.94582390785217</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
